--- a/data/trans_dic/P2A_R-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P2A_R-Provincia-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas con alguna limitación</t>
+          <t>Hogares con personas con alguna limitación (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -638,7 +639,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -716,69 +717,69 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>16,7; 35,86</t>
+          <t>16,88; 36,95</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>26,26; 56,07</t>
+          <t>27,23; 56,88</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>30,04; 53,82</t>
+          <t>30,1; 54,06</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>34,26; 58,28</t>
+          <t>33,32; 58,39</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>21,23; 42,27</t>
+          <t>21,97; 43,95</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>24,35; 51,94</t>
+          <t>25,4; 53,12</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>34,64; 59,0</t>
+          <t>35,72; 59,3</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>38,7; 59,77</t>
+          <t>38,2; 58,92</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>22,12; 36,9</t>
+          <t>22,47; 35,98</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>29,32; 49,29</t>
+          <t>29,2; 49,34</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>36,77; 52,88</t>
+          <t>36,42; 52,83</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>40,01; 56,36</t>
+          <t>39,58; 56,16</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -856,69 +857,69 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>27,79; 46,11</t>
+          <t>27,57; 46,12</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>27,33; 48,02</t>
+          <t>26,73; 47,84</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>29,96; 49,25</t>
+          <t>30,37; 49,44</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>75,99; 92,91</t>
+          <t>76,05; 92,64</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>37,1; 55,73</t>
+          <t>36,82; 56,83</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>27,37; 47,6</t>
+          <t>27,17; 47,45</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>23,38; 39,45</t>
+          <t>23,29; 40,86</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>66,26; 86,06</t>
+          <t>66,3; 85,41</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>34,71; 48,71</t>
+          <t>34,73; 48,44</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>29,34; 43,76</t>
+          <t>29,92; 43,89</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>28,49; 41,15</t>
+          <t>28,2; 41,27</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>73,43; 87,11</t>
+          <t>73,88; 87,39</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>18,23; 36,34</t>
+          <t>19,03; 37,21</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>28,7; 51,47</t>
+          <t>28,39; 50,62</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>19,7; 40,59</t>
+          <t>19,62; 40,03</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>62,56; 80,76</t>
+          <t>61,82; 80,99</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>19,32; 35,16</t>
+          <t>19,22; 36,8</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>23,88; 43,33</t>
+          <t>23,07; 43,22</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>21,28; 40,76</t>
+          <t>20,07; 39,36</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>65,86; 83,07</t>
+          <t>66,17; 83,17</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>21,37; 33,44</t>
+          <t>20,66; 33,08</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>28,33; 43,51</t>
+          <t>28,38; 43,49</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>23,25; 36,46</t>
+          <t>22,39; 36,56</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>67,61; 80,3</t>
+          <t>67,79; 80,13</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>27,14; 45,68</t>
+          <t>27,03; 45,25</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>28,74; 53,14</t>
+          <t>28,65; 51,79</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>27,27; 52,86</t>
+          <t>28,81; 52,45</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>62,15; 81,78</t>
+          <t>61,47; 81,61</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>31,29; 50,24</t>
+          <t>31,6; 49,38</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>24,84; 47,78</t>
+          <t>24,6; 47,06</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>22,75; 46,94</t>
+          <t>23,96; 47,64</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>32,56; 72,7</t>
+          <t>35,1; 74,12</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>31,93; 45,2</t>
+          <t>31,77; 45,34</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>30,33; 46,24</t>
+          <t>29,94; 46,43</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>29,48; 45,81</t>
+          <t>29,07; 45,84</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>48,46; 74,03</t>
+          <t>48,97; 73,65</t>
         </is>
       </c>
     </row>
@@ -1276,69 +1277,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>22,15; 78,3</t>
+          <t>22,98; 78,42</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>26,43; 66,9</t>
+          <t>26,69; 67,7</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>25,93; 54,26</t>
+          <t>25,91; 53,33</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>90,04; 100,0</t>
+          <t>90,32; 100,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,34; 54,21</t>
+          <t>8,41; 53,24</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,16; 48,72</t>
+          <t>18,21; 48,83</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>26,34; 51,81</t>
+          <t>25,81; 51,93</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>78,9; 98,56</t>
+          <t>79,36; 98,57</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>22,62; 57,18</t>
+          <t>20,78; 56,78</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>25,73; 53,07</t>
+          <t>26,54; 52,24</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>28,75; 49,05</t>
+          <t>29,93; 49,23</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>86,03; 98,13</t>
+          <t>86,7; 98,4</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1416,69 +1417,69 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>13,88; 34,04</t>
+          <t>14,07; 33,05</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>30,09; 55,23</t>
+          <t>29,35; 53,71</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>26,0; 55,72</t>
+          <t>26,05; 57,17</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>56,34; 77,07</t>
+          <t>55,64; 77,2</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>25,6; 47,6</t>
+          <t>26,0; 47,4</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>28,87; 52,74</t>
+          <t>29,28; 53,02</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>23,14; 51,67</t>
+          <t>21,89; 53,55</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>60,33; 80,39</t>
+          <t>61,73; 79,96</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>22,84; 37,21</t>
+          <t>22,81; 36,64</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>32,24; 49,54</t>
+          <t>32,7; 49,65</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>27,86; 49,75</t>
+          <t>28,66; 48,77</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>62,16; 76,25</t>
+          <t>62,01; 76,2</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1556,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>25,53; 39,73</t>
+          <t>25,23; 39,21</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>29,15; 43,98</t>
+          <t>28,41; 44,1</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>20,62; 34,38</t>
+          <t>21,6; 35,17</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>78,65; 89,94</t>
+          <t>78,35; 89,14</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>29,41; 43,91</t>
+          <t>29,5; 43,72</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>29,52; 43,76</t>
+          <t>29,91; 45,06</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>22,35; 36,08</t>
+          <t>22,66; 36,34</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>70,25; 88,38</t>
+          <t>70,87; 88,15</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>29,41; 40,49</t>
+          <t>29,41; 39,77</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>31,19; 41,83</t>
+          <t>31,49; 42,1</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>23,53; 33,26</t>
+          <t>23,83; 33,54</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>77,21; 87,67</t>
+          <t>77,27; 87,65</t>
         </is>
       </c>
     </row>
@@ -1696,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>32,86; 48,66</t>
+          <t>32,85; 49,48</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>18,29; 30,69</t>
+          <t>18,86; 32,21</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>25,85; 38,32</t>
+          <t>25,48; 38,63</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>81,56; 90,98</t>
+          <t>81,57; 91,13</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>34,22; 50,03</t>
+          <t>34,31; 49,67</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>25,38; 39,03</t>
+          <t>25,09; 38,71</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>26,34; 39,12</t>
+          <t>26,64; 39,07</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>80,32; 90,41</t>
+          <t>79,89; 90,39</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>35,8; 47,39</t>
+          <t>35,59; 46,92</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>23,93; 33,02</t>
+          <t>23,51; 33,39</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>27,96; 37,1</t>
+          <t>27,61; 36,61</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>82,46; 89,61</t>
+          <t>82,77; 89,62</t>
         </is>
       </c>
     </row>
@@ -1836,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>29,64; 36,33</t>
+          <t>29,7; 36,21</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>31,76; 39,16</t>
+          <t>32,1; 39,38</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>30,69; 37,3</t>
+          <t>31,04; 37,85</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>74,65; 81,5</t>
+          <t>74,32; 81,25</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>33,89; 40,4</t>
+          <t>33,88; 40,4</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>31,81; 38,71</t>
+          <t>32,03; 38,66</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>30,28; 36,87</t>
+          <t>30,35; 36,4</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>71,22; 78,63</t>
+          <t>71,37; 79,07</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>32,83; 37,65</t>
+          <t>32,76; 37,45</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>32,69; 37,54</t>
+          <t>32,85; 37,92</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>31,33; 36,24</t>
+          <t>31,23; 35,92</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>73,89; 79,25</t>
+          <t>74,12; 79,18</t>
         </is>
       </c>
     </row>
@@ -1920,4 +1921,2040 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Hogares con personas con alguna limitación (tasa de respuesta: 100,0%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Almería</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>12163</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>10382</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>19004</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>34449</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>16173</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>14430</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>24371</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>38942</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>28336</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>24813</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>43375</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>73390</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>8051; 17629</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>6904; 14424</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>13660; 24537</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>24421; 42792</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>11239; 22485</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>9671; 20228</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>18571; 30833</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>30318; 46765</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>22219; 35569</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>18523; 31298</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>35468; 51445</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>60423; 85727</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Cádiz</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>243</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>24513</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>19812</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>27858</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>106634</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>30142</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>21729</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>24867</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>100109</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>54654</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>41541</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>52725</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>206743</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>18718; 31310</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>14537; 26017</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>21472; 34953</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>97076; 118253</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>23911; 36904</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>15997; 27942</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>18634; 32684</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>84594; 108985</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>46130; 64340</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>33888; 49711</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>42498; 62191</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>188586; 223069</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>147</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>17487</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>20614</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>17001</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>42191</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>18177</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>19475</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>19506</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>50707</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>35664</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>40089</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>36506</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>92898</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>12313; 24076</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>14965; 26683</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>11403; 23265</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>36021; 47190</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>13048; 24987</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>13824; 25901</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>13285; 26049</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>44439; 55857</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>27389; 43870</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>31967; 48987</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>27825; 45446</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>85031; 100503</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Granada</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>117</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>23996</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>20363</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>17999</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>50492</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>29979</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>19736</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>16652</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>45788</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>53975</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>40099</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>34651</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>96281</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>17856; 29887</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>14234; 25727</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>12997; 23661</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>43116; 57245</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>23234; 36299</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>13648; 26105</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>11419; 22701</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>27425; 57916</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>44339; 63285</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>31478; 48827</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>26968; 42524</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>72610; 109206</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Huelva</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>134</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>4831</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>8485</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>12799</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>33549</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>3007</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>7801</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>13515</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>37950</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>7838</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>16286</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>26313</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>71499</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>2192; 7482</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>4815; 12216</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>8390; 17266</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>31172; 34513</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>959; 6069</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>4484; 12027</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>9166; 18444</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>32315; 40135</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>4352; 11891</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>11324; 22290</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>20319; 33425</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>65225; 74030</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>Jaén</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>10560</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>18437</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>11064</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>31108</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>18982</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>20221</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>11376</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>39980</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>29541</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>38657</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>22440</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>71089</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>6565; 15420</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>13074; 23922</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>7108; 15597</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>25688; 35640</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>13588; 24779</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>14504; 26260</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>6863; 16791</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>34682; 44926</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>22561; 36243</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>30764; 46712</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>16808; 28596</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>63473; 77991</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Málaga</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>149</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>299</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>35724</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>42482</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>32263</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>105556</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>40431</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>44849</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>34774</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>128476</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>76156</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>87331</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>67037</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>234032</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>27914; 43383</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>33160; 51462</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>25225; 41065</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>97550; 110982</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>32684; 48436</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>36421; 54871</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>26992; 43287</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>110571; 137520</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>65120; 88071</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>75094; 100398</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>56207; 79125</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>216753; 245889</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>164</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>179</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>134</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>343</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n"/>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>36363</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>28495</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>41157</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>114765</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>40319</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>41077</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>45283</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>134497</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>76682</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>69572</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>86441</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>249262</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n"/>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>29619; 44618</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>21795; 37219</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>33039; 50079</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>107362; 119950</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>33134; 47971</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>32731; 50500</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>37087; 54393</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>125264; 141723</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>66458; 87628</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>57838; 82150</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>74237; 98449</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>238711; 258467</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>246</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>241</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>266</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>731</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>297</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>270</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>277</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>765</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>543</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>511</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>543</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>1496</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n"/>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>165636</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>169071</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>179144</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>518745</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>197211</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>189318</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>190343</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>576450</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>362846</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>358388</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>369487</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>1095195</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n"/>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>149513; 182265</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>153090; 187837</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>163082; 198848</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>495054; 541281</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>179082; 213526</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>172586; 208284</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>173316; 207870</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>543841; 602518</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>338020; 386435</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>333641; 385221</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>342393; 393868</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>1058540; 1130723</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A25:A27"/>
+    <mergeCell ref="A28:A30"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/P2A_R-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P2A_R-Provincia-trans_dic.xlsx
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>16,88; 36,95</t>
+          <t>17,03; 37,38</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>27,23; 56,88</t>
+          <t>27,39; 56,53</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>30,1; 54,06</t>
+          <t>30,55; 52,51</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>33,32; 58,39</t>
+          <t>33,81; 58,99</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>21,97; 43,95</t>
+          <t>22,13; 44,41</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>25,4; 53,12</t>
+          <t>24,12; 51,95</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>35,72; 59,3</t>
+          <t>35,15; 57,94</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>38,2; 58,92</t>
+          <t>39,48; 59,83</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>22,47; 35,98</t>
+          <t>21,77; 37,29</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>29,2; 49,34</t>
+          <t>29,8; 48,67</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>36,42; 52,83</t>
+          <t>36,82; 53,36</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>39,58; 56,16</t>
+          <t>39,55; 56,75</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>27,57; 46,12</t>
+          <t>26,72; 45,51</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>26,73; 47,84</t>
+          <t>26,39; 47,59</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>30,37; 49,44</t>
+          <t>30,2; 49,47</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>76,05; 92,64</t>
+          <t>76,16; 93,03</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>36,82; 56,83</t>
+          <t>36,62; 55,84</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>27,17; 47,45</t>
+          <t>26,27; 46,85</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>23,29; 40,86</t>
+          <t>23,17; 39,8</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>66,3; 85,41</t>
+          <t>67,92; 85,86</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>34,73; 48,44</t>
+          <t>34,45; 48,49</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>29,92; 43,89</t>
+          <t>29,52; 44,01</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>28,2; 41,27</t>
+          <t>28,74; 41,88</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>73,88; 87,39</t>
+          <t>74,14; 87,35</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>19,03; 37,21</t>
+          <t>18,61; 37,39</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>28,39; 50,62</t>
+          <t>27,61; 50,16</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>19,62; 40,03</t>
+          <t>19,63; 39,76</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>61,82; 80,99</t>
+          <t>62,1; 80,75</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>19,22; 36,8</t>
+          <t>19,32; 35,85</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>23,07; 43,22</t>
+          <t>23,12; 43,44</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>20,07; 39,36</t>
+          <t>20,93; 38,34</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>66,17; 83,17</t>
+          <t>66,15; 83,5</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>20,66; 33,08</t>
+          <t>21,16; 33,74</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>28,38; 43,49</t>
+          <t>28,66; 43,71</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>22,39; 36,56</t>
+          <t>22,41; 36,08</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>67,79; 80,13</t>
+          <t>67,61; 80,3</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>27,03; 45,25</t>
+          <t>27,35; 46,56</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>28,65; 51,79</t>
+          <t>30,5; 52,94</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>28,81; 52,45</t>
+          <t>28,77; 51,94</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>61,47; 81,61</t>
+          <t>60,86; 80,34</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>31,6; 49,38</t>
+          <t>30,84; 49,86</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>24,6; 47,06</t>
+          <t>23,79; 46,15</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>23,96; 47,64</t>
+          <t>24,1; 47,72</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>35,1; 74,12</t>
+          <t>31,49; 72,96</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>31,77; 45,34</t>
+          <t>32,51; 45,59</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>29,94; 46,43</t>
+          <t>30,82; 47,65</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>29,07; 45,84</t>
+          <t>28,85; 45,9</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>48,97; 73,65</t>
+          <t>47,04; 73,27</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>22,98; 78,42</t>
+          <t>22,41; 79,24</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>26,69; 67,7</t>
+          <t>28,64; 68,79</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>25,91; 53,33</t>
+          <t>26,41; 53,75</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>90,32; 100,0</t>
+          <t>90,04; 100,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>8,41; 53,24</t>
+          <t>12,01; 56,94</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>18,21; 48,83</t>
+          <t>17,21; 49,24</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>25,81; 51,93</t>
+          <t>26,22; 52,83</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>79,36; 98,57</t>
+          <t>79,31; 98,56</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>20,78; 56,78</t>
+          <t>22,62; 55,05</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>26,54; 52,24</t>
+          <t>24,99; 51,57</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>29,93; 49,23</t>
+          <t>29,28; 48,4</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>86,7; 98,4</t>
+          <t>87,76; 98,44</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>14,07; 33,05</t>
+          <t>13,94; 32,89</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>29,35; 53,71</t>
+          <t>28,97; 53,81</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>26,05; 57,17</t>
+          <t>26,4; 56,96</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>55,64; 77,2</t>
+          <t>56,02; 77,32</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>26,0; 47,4</t>
+          <t>26,29; 47,01</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>29,28; 53,02</t>
+          <t>29,44; 53,58</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>21,89; 53,55</t>
+          <t>23,9; 52,83</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>61,73; 79,96</t>
+          <t>60,84; 79,83</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>22,81; 36,64</t>
+          <t>22,67; 37,11</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>32,7; 49,65</t>
+          <t>32,15; 49,58</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>28,66; 48,77</t>
+          <t>28,95; 49,38</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>62,01; 76,2</t>
+          <t>62,21; 76,8</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>25,23; 39,21</t>
+          <t>25,9; 39,9</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>28,41; 44,1</t>
+          <t>28,58; 44,23</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>21,6; 35,17</t>
+          <t>21,11; 34,89</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>78,35; 89,14</t>
+          <t>78,51; 89,51</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>29,5; 43,72</t>
+          <t>30,24; 44,1</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>29,91; 45,06</t>
+          <t>29,71; 44,27</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>22,66; 36,34</t>
+          <t>22,66; 36,23</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>70,87; 88,15</t>
+          <t>71,67; 88,35</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>29,41; 39,77</t>
+          <t>29,25; 39,6</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>31,49; 42,1</t>
+          <t>31,32; 41,73</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>23,83; 33,54</t>
+          <t>24,03; 33,53</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>77,27; 87,65</t>
+          <t>76,85; 87,64</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>32,85; 49,48</t>
+          <t>32,35; 48,29</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>18,86; 32,21</t>
+          <t>19,06; 31,7</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>25,48; 38,63</t>
+          <t>25,43; 37,48</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>81,57; 91,13</t>
+          <t>81,9; 91,12</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>34,31; 49,67</t>
+          <t>34,01; 49,57</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>25,09; 38,71</t>
+          <t>25,5; 38,27</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>26,64; 39,07</t>
+          <t>26,56; 39,01</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>79,89; 90,39</t>
+          <t>80,12; 90,39</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>35,59; 46,92</t>
+          <t>35,21; 47,01</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>23,51; 33,39</t>
+          <t>23,85; 33,2</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>27,61; 36,61</t>
+          <t>27,61; 36,85</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>82,77; 89,62</t>
+          <t>82,47; 89,53</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>29,7; 36,21</t>
+          <t>29,43; 36,18</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>32,1; 39,38</t>
+          <t>32,1; 39,04</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>31,04; 37,85</t>
+          <t>30,92; 37,92</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>74,32; 81,25</t>
+          <t>74,28; 81,43</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>33,88; 40,4</t>
+          <t>33,95; 40,57</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>32,03; 38,66</t>
+          <t>32,02; 38,67</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>30,35; 36,4</t>
+          <t>29,68; 36,41</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>71,37; 79,07</t>
+          <t>71,53; 78,96</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>32,76; 37,45</t>
+          <t>32,73; 37,63</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>32,85; 37,92</t>
+          <t>32,81; 37,88</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>31,23; 35,92</t>
+          <t>31,59; 36,2</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>74,12; 79,18</t>
+          <t>73,79; 78,81</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>8051; 17629</t>
+          <t>8126; 17833</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>6904; 14424</t>
+          <t>6944; 14334</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>13660; 24537</t>
+          <t>13863; 23834</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>24421; 42792</t>
+          <t>24776; 43226</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>11239; 22485</t>
+          <t>11324; 22720</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>9671; 20228</t>
+          <t>9185; 19783</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>18571; 30833</t>
+          <t>18273; 30123</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>30318; 46765</t>
+          <t>31333; 47488</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>22219; 35569</t>
+          <t>21529; 36867</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>18523; 31298</t>
+          <t>18905; 30874</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>35468; 51445</t>
+          <t>35858; 51958</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>60423; 85727</t>
+          <t>60373; 86629</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>18718; 31310</t>
+          <t>18140; 30893</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>14537; 26017</t>
+          <t>14354; 25881</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>21472; 34953</t>
+          <t>21351; 34978</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>97076; 118253</t>
+          <t>97218; 118758</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>23911; 36904</t>
+          <t>23777; 36259</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>15997; 27942</t>
+          <t>15469; 27589</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>18634; 32684</t>
+          <t>18532; 31839</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>84594; 108985</t>
+          <t>86665; 109554</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>46130; 64340</t>
+          <t>45761; 64403</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>33888; 49711</t>
+          <t>33440; 49846</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>42498; 62191</t>
+          <t>43316; 63111</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>188586; 223069</t>
+          <t>189233; 222963</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>12313; 24076</t>
+          <t>12039; 24192</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>14965; 26683</t>
+          <t>14556; 26440</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>11403; 23265</t>
+          <t>11410; 23105</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>36021; 47190</t>
+          <t>36182; 47054</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>13048; 24987</t>
+          <t>13119; 24346</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>13824; 25901</t>
+          <t>13858; 26037</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>13285; 26049</t>
+          <t>13853; 25371</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>44439; 55857</t>
+          <t>44428; 56082</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>27389; 43870</t>
+          <t>28062; 44739</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>31967; 48987</t>
+          <t>32280; 49235</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>27825; 45446</t>
+          <t>27857; 44840</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>85031; 100503</t>
+          <t>84808; 100723</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>17856; 29887</t>
+          <t>18064; 30753</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>14234; 25727</t>
+          <t>15154; 26303</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>12997; 23661</t>
+          <t>12980; 23431</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>43116; 57245</t>
+          <t>42692; 56353</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>23234; 36299</t>
+          <t>22672; 36656</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>13648; 26105</t>
+          <t>13198; 25600</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>11419; 22701</t>
+          <t>11486; 22739</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>27425; 57916</t>
+          <t>24604; 57004</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>44339; 63285</t>
+          <t>45381; 63629</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>31478; 48827</t>
+          <t>32412; 50107</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>26968; 42524</t>
+          <t>26759; 42575</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>72610; 109206</t>
+          <t>69745; 108650</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>2192; 7482</t>
+          <t>2138; 7560</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>4815; 12216</t>
+          <t>5167; 12412</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>8390; 17266</t>
+          <t>8551; 17402</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>31172; 34513</t>
+          <t>31075; 34513</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>959; 6069</t>
+          <t>1369; 6490</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4484; 12027</t>
+          <t>4238; 12127</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>9166; 18444</t>
+          <t>9314; 18762</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>32315; 40135</t>
+          <t>32294; 40131</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>4352; 11891</t>
+          <t>4737; 11528</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>11324; 22290</t>
+          <t>10664; 22005</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>20319; 33425</t>
+          <t>19878; 32858</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>65225; 74030</t>
+          <t>66024; 74055</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>6565; 15420</t>
+          <t>6506; 15346</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>13074; 23922</t>
+          <t>12903; 23969</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>7108; 15597</t>
+          <t>7202; 15540</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>25688; 35640</t>
+          <t>25863; 35698</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>13588; 24779</t>
+          <t>13743; 24573</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>14504; 26260</t>
+          <t>14584; 26540</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>6863; 16791</t>
+          <t>7496; 16565</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>34682; 44926</t>
+          <t>34182; 44853</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>22561; 36243</t>
+          <t>22432; 36715</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>30764; 46712</t>
+          <t>30243; 46642</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>16808; 28596</t>
+          <t>16977; 28954</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>63473; 77991</t>
+          <t>63672; 78607</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>27914; 43383</t>
+          <t>28661; 44147</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>33160; 51462</t>
+          <t>33360; 51616</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>25225; 41065</t>
+          <t>24645; 40735</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>97550; 110982</t>
+          <t>97750; 111447</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>32684; 48436</t>
+          <t>33501; 48856</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>36421; 54871</t>
+          <t>36178; 53913</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>26992; 43287</t>
+          <t>26991; 43159</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>110571; 137520</t>
+          <t>111817; 137844</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>65120; 88071</t>
+          <t>64780; 87678</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>75094; 100398</t>
+          <t>74690; 99518</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>56207; 79125</t>
+          <t>56673; 79084</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>216753; 245889</t>
+          <t>215586; 245856</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>29619; 44618</t>
+          <t>29172; 43537</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>21795; 37219</t>
+          <t>22026; 36628</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>33039; 50079</t>
+          <t>32972; 48599</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>107362; 119950</t>
+          <t>107796; 119934</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>33134; 47971</t>
+          <t>32851; 47875</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>32731; 50500</t>
+          <t>33265; 49934</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>37087; 54393</t>
+          <t>36978; 54310</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>125264; 141723</t>
+          <t>125631; 141720</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>66458; 87628</t>
+          <t>65761; 87781</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>57838; 82150</t>
+          <t>58678; 81669</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>74237; 98449</t>
+          <t>74248; 99074</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>238711; 258467</t>
+          <t>237850; 258227</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>149513; 182265</t>
+          <t>148119; 182107</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>153090; 187837</t>
+          <t>153097; 186219</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>163082; 198848</t>
+          <t>162427; 199215</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>495054; 541281</t>
+          <t>494793; 542431</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>179082; 213526</t>
+          <t>179464; 214454</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>172586; 208284</t>
+          <t>172497; 208367</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>173316; 207870</t>
+          <t>169476; 207926</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>543841; 602518</t>
+          <t>545068; 601628</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>338020; 386435</t>
+          <t>337770; 388260</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>333641; 385221</t>
+          <t>333254; 384731</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>342393; 393868</t>
+          <t>346326; 396908</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>1058540; 1130723</t>
+          <t>1053870; 1125460</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P2A_R-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P2A_R-Provincia-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>31,61%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>37,89%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>46,87%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>47,98%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>25,49%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>40,94%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>41,87%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>47,01%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>31,61%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>37,89%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>46,87%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>49,07%</t>
+          <t>43,88%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>48,08%</t>
+          <t>46,06%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>17,03; 37,38</t>
+          <t>21,23; 42,27</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>27,39; 56,53</t>
+          <t>24,35; 51,94</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>30,55; 52,51</t>
+          <t>34,64; 59,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>33,81; 58,99</t>
+          <t>37,14; 58,06</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>22,13; 44,41</t>
+          <t>16,7; 35,86</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>24,12; 51,95</t>
+          <t>26,26; 56,07</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>35,15; 57,94</t>
+          <t>30,04; 53,82</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>39,48; 59,83</t>
+          <t>33,2; 53,45</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>21,77; 37,29</t>
+          <t>22,12; 36,9</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>29,8; 48,67</t>
+          <t>29,32; 49,29</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>36,82; 53,36</t>
+          <t>36,77; 52,88</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>39,55; 56,75</t>
+          <t>39,09; 53,02</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>46,42%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>36,9%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>31,09%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>78,76%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>36,11%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>36,43%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>39,4%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>83,53%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>46,42%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>36,9%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>31,09%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>78,46%</t>
+          <t>78,89%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>81,0%</t>
+          <t>78,82%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>26,72; 45,51</t>
+          <t>37,1; 55,73</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>26,39; 47,59</t>
+          <t>27,37; 47,6</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>30,2; 49,47</t>
+          <t>23,38; 39,45</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>76,16; 93,03</t>
+          <t>67,47; 86,44</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>36,62; 55,84</t>
+          <t>27,79; 46,11</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>26,27; 46,85</t>
+          <t>27,33; 48,02</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>23,17; 39,8</t>
+          <t>29,96; 49,25</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>67,92; 85,86</t>
+          <t>70,91; 86,44</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>34,45; 48,49</t>
+          <t>34,71; 48,71</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>29,52; 44,01</t>
+          <t>29,34; 43,76</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>28,74; 41,88</t>
+          <t>28,49; 41,15</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>74,14; 87,35</t>
+          <t>71,37; 83,85</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>26,77%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>32,49%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>29,48%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>75,42%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>27,03%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>39,11%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>29,25%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>72,41%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>26,77%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>32,49%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>29,48%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>75,5%</t>
+          <t>72,21%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>74,06%</t>
+          <t>73,85%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>18,61; 37,39</t>
+          <t>19,32; 35,16</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>27,61; 50,16</t>
+          <t>23,88; 43,33</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>19,63; 39,76</t>
+          <t>21,28; 40,76</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>62,1; 80,75</t>
+          <t>65,62; 82,95</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>19,32; 35,85</t>
+          <t>18,23; 36,34</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>23,12; 43,44</t>
+          <t>28,7; 51,47</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>20,93; 38,34</t>
+          <t>19,7; 40,59</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>66,15; 83,5</t>
+          <t>62,23; 80,55</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>21,16; 33,74</t>
+          <t>21,37; 33,44</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>28,66; 43,71</t>
+          <t>28,33; 43,51</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>22,41; 36,08</t>
+          <t>23,25; 36,46</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>67,61; 80,3</t>
+          <t>67,52; 80,07</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>40,78%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>35,58%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>34,95%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>60,06%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>36,33%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>40,99%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>39,9%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>71,98%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>40,78%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>35,58%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>34,95%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>58,6%</t>
+          <t>72,53%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>64,93%</t>
+          <t>66,24%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>27,35; 46,56</t>
+          <t>31,29; 50,24</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>30,5; 52,94</t>
+          <t>24,84; 47,78</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>28,77; 51,94</t>
+          <t>22,75; 46,94</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>60,86; 80,34</t>
+          <t>36,28; 74,17</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>30,84; 49,86</t>
+          <t>27,14; 45,68</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>23,79; 46,15</t>
+          <t>28,74; 53,14</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>24,1; 47,72</t>
+          <t>27,27; 52,86</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>31,49; 72,96</t>
+          <t>62,93; 82,38</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>32,51; 45,59</t>
+          <t>31,93; 45,2</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>30,82; 47,65</t>
+          <t>30,33; 46,24</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>28,85; 45,9</t>
+          <t>29,48; 45,81</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>47,04; 73,27</t>
+          <t>51,66; 75,12</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>26,38%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>31,67%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>38,05%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>95,44%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>50,63%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>47,03%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>39,53%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>97,21%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>26,38%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>31,67%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>38,05%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>93,2%</t>
+          <t>97,41%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>95,04%</t>
+          <t>96,37%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>22,41; 79,24</t>
+          <t>6,34; 54,21</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>28,64; 68,79</t>
+          <t>17,16; 48,72</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>26,41; 53,75</t>
+          <t>26,34; 51,81</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>90,04; 100,0</t>
+          <t>88,29; 98,62</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>12,01; 56,94</t>
+          <t>22,15; 78,3</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,21; 49,24</t>
+          <t>26,43; 66,9</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>26,22; 52,83</t>
+          <t>25,93; 54,26</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>79,31; 98,56</t>
+          <t>90,86; 100,0</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>22,62; 55,05</t>
+          <t>22,62; 57,18</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>24,99; 51,57</t>
+          <t>25,73; 53,07</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>29,28; 48,4</t>
+          <t>28,75; 49,05</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>87,76; 98,44</t>
+          <t>91,58; 98,69</t>
         </is>
       </c>
     </row>
@@ -1349,42 +1349,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>36,31%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>40,82%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>36,28%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>70,64%</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>22,63%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>41,39%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>40,55%</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>67,38%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>36,31%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>40,82%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>36,28%</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>71,16%</t>
+          <t>66,38%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>69,45%</t>
+          <t>68,58%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>13,94; 32,89</t>
+          <t>25,6; 47,6</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>28,97; 53,81</t>
+          <t>28,87; 52,74</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>26,4; 56,96</t>
+          <t>23,14; 51,67</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>56,02; 77,32</t>
+          <t>59,83; 80,27</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>26,29; 47,01</t>
+          <t>13,88; 34,04</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>29,44; 53,58</t>
+          <t>30,09; 55,23</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>23,9; 52,83</t>
+          <t>26,0; 55,72</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>60,84; 79,83</t>
+          <t>55,0; 76,42</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>22,67; 37,11</t>
+          <t>22,84; 37,21</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>32,15; 49,58</t>
+          <t>32,24; 49,54</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>28,95; 49,38</t>
+          <t>27,86; 49,75</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>62,21; 76,8</t>
+          <t>61,27; 75,8</t>
         </is>
       </c>
     </row>
@@ -1489,42 +1489,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>36,49%</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>36,83%</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>29,19%</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>84,66%</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>32,29%</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>36,4%</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>27,63%</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>84,78%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>36,49%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>36,83%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>29,19%</t>
-        </is>
-      </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>82,35%</t>
+          <t>84,01%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>83,43%</t>
+          <t>84,36%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>25,9; 39,9</t>
+          <t>29,41; 43,91</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>28,58; 44,23</t>
+          <t>29,52; 43,76</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>21,11; 34,89</t>
+          <t>22,35; 36,08</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>78,51; 89,51</t>
+          <t>78,53; 89,9</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>30,24; 44,1</t>
+          <t>25,53; 39,73</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>29,71; 44,27</t>
+          <t>29,15; 43,98</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>22,66; 36,23</t>
+          <t>20,62; 34,38</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>71,67; 88,35</t>
+          <t>77,54; 89,57</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>29,25; 39,6</t>
+          <t>29,41; 40,49</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>31,32; 41,73</t>
+          <t>31,19; 41,83</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>24,03; 33,53</t>
+          <t>23,53; 33,26</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>76,85; 87,64</t>
+          <t>80,23; 88,18</t>
         </is>
       </c>
     </row>
@@ -1629,42 +1629,42 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>41,75%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>31,48%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>32,53%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>85,86%</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
           <t>40,33%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>24,66%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="I18" s="2" t="inlineStr">
         <is>
           <t>31,74%</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>87,19%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>41,75%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>31,48%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>32,53%</t>
-        </is>
-      </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>85,78%</t>
+          <t>87,48%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>86,43%</t>
+          <t>86,62%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>32,35; 48,29</t>
+          <t>34,22; 50,03</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>19,06; 31,7</t>
+          <t>25,38; 39,03</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>25,43; 37,48</t>
+          <t>26,34; 39,12</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>81,9; 91,12</t>
+          <t>80,21; 90,35</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>34,01; 49,57</t>
+          <t>32,86; 48,66</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>25,5; 38,27</t>
+          <t>18,29; 30,69</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>26,56; 39,01</t>
+          <t>25,85; 38,32</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>80,12; 90,39</t>
+          <t>81,91; 91,31</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>35,21; 47,01</t>
+          <t>35,8; 47,39</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>23,85; 33,2</t>
+          <t>23,93; 33,02</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>27,61; 36,85</t>
+          <t>27,96; 37,1</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>82,47; 89,53</t>
+          <t>82,55; 89,84</t>
         </is>
       </c>
     </row>
@@ -1769,42 +1769,42 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>37,31%</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>35,14%</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>33,33%</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>76,91%</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>32,91%</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>35,45%</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>34,1%</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>77,87%</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>37,31%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>35,14%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>33,33%</t>
-        </is>
-      </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>75,65%</t>
+          <t>77,49%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>76,69%</t>
+          <t>77,18%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>29,43; 36,18</t>
+          <t>33,89; 40,4</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>32,1; 39,04</t>
+          <t>31,81; 38,71</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>30,92; 37,92</t>
+          <t>30,28; 36,87</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>74,28; 81,43</t>
+          <t>73,12; 79,8</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>33,95; 40,57</t>
+          <t>29,64; 36,33</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>32,02; 38,67</t>
+          <t>31,76; 39,16</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>29,68; 36,41</t>
+          <t>30,69; 37,3</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>71,53; 78,96</t>
+          <t>74,71; 80,23</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>32,73; 37,63</t>
+          <t>32,83; 37,65</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>32,81; 37,88</t>
+          <t>32,69; 37,54</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>31,59; 36,2</t>
+          <t>31,33; 36,24</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>73,79; 78,81</t>
+          <t>74,89; 79,3</t>
         </is>
       </c>
     </row>
@@ -1957,7 +1957,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1965,7 +1965,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -2073,42 +2073,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>44</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>49</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -2141,42 +2141,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>16173</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>14430</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>24371</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>30779</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>12163</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>10382</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>19004</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>34449</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>16173</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>14430</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>24371</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>38942</t>
+          <t>24783</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>73390</t>
+          <t>55562</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>8126; 17833</t>
+          <t>10863; 21627</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>6944; 14334</t>
+          <t>9272; 19778</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>13863; 23834</t>
+          <t>18010; 30678</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>24776; 43226</t>
+          <t>23824; 37241</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>11324; 22720</t>
+          <t>7966; 17110</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>9185; 19783</t>
+          <t>6659; 14216</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>18273; 30123</t>
+          <t>13636; 24426</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>31333; 47488</t>
+          <t>18753; 30189</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>21529; 36867</t>
+          <t>21869; 36484</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>18905; 30874</t>
+          <t>18601; 31268</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>35858; 51958</t>
+          <t>35807; 51491</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>60373; 86629</t>
+          <t>47150; 63962</t>
         </is>
       </c>
     </row>
@@ -2281,42 +2281,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
           <t>37</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>113</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>130</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -2349,42 +2349,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>30142</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>21729</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>24867</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>91227</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>24513</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>19812</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>27858</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>106634</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>30142</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>21729</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>24867</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>100109</t>
+          <t>79987</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>206743</t>
+          <t>171215</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>18140; 30893</t>
+          <t>24093; 36185</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>14354; 25881</t>
+          <t>16117; 28031</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>21351; 34978</t>
+          <t>18702; 31558</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>97218; 118758</t>
+          <t>78153; 100131</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>23777; 36259</t>
+          <t>18864; 31301</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>15469; 27589</t>
+          <t>14863; 26115</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>18532; 31839</t>
+          <t>21180; 34818</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>86665; 109554</t>
+          <t>71903; 87651</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>45761; 64403</t>
+          <t>46095; 64692</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>33440; 49846</t>
+          <t>33233; 49565</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>43316; 63111</t>
+          <t>42929; 62012</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>189233; 222963</t>
+          <t>155030; 182156</t>
         </is>
       </c>
     </row>
@@ -2489,42 +2489,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>24</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>71</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>76</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -2557,42 +2557,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>18177</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>19475</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>19506</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>44784</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>17487</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>20614</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>17001</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>42191</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>18177</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>19475</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>19506</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>50707</t>
+          <t>40839</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>92898</t>
+          <t>85625</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>12039; 24192</t>
+          <t>13118; 23876</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>14556; 26440</t>
+          <t>14315; 25968</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>11410; 23105</t>
+          <t>14084; 26972</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>36182; 47054</t>
+          <t>38965; 49254</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>13119; 24346</t>
+          <t>11794; 23510</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>13858; 26037</t>
+          <t>15126; 27133</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>13853; 25371</t>
+          <t>11449; 23587</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>44428; 56082</t>
+          <t>35196; 45559</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>28062; 44739</t>
+          <t>28342; 44337</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>32280; 49235</t>
+          <t>31915; 49017</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>27857; 44840</t>
+          <t>28894; 45314</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>84808; 100723</t>
+          <t>78285; 92828</t>
         </is>
       </c>
     </row>
@@ -2697,42 +2697,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>36</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>70</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>47</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2765,42 +2765,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>29979</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>19736</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>16652</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>43343</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>23996</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>20363</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>17999</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>50492</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>29979</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>19736</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>16652</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>45788</t>
+          <t>51381</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>96281</t>
+          <t>94723</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>18064; 30753</t>
+          <t>23001; 36934</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>15154; 26303</t>
+          <t>13778; 26504</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>12980; 23431</t>
+          <t>10840; 22366</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>42692; 56353</t>
+          <t>26181; 53520</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>22672; 36656</t>
+          <t>17924; 30175</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>13198; 25600</t>
+          <t>14277; 26400</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>11486; 22739</t>
+          <t>12303; 23848</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>24604; 57004</t>
+          <t>44581; 58360</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>45381; 63629</t>
+          <t>44571; 63082</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>32412; 50107</t>
+          <t>31897; 48623</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>26759; 42575</t>
+          <t>27345; 42499</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>69745; 108650</t>
+          <t>73873; 107419</t>
         </is>
       </c>
     </row>
@@ -2905,42 +2905,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>66</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>68</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2973,42 +2973,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>3007</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>7801</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>13515</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>37773</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>4831</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>8485</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>12799</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>33549</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>3007</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>7801</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>13515</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>37950</t>
+          <t>34687</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>71499</t>
+          <t>72460</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>2138; 7560</t>
+          <t>723; 6179</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>5167; 12412</t>
+          <t>4226; 12000</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>8551; 17402</t>
+          <t>9354; 18400</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>31075; 34513</t>
+          <t>34944; 39034</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>1369; 6490</t>
+          <t>2113; 7471</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4238; 12127</t>
+          <t>4768; 12070</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>9314; 18762</t>
+          <t>8394; 17567</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>32294; 40131</t>
+          <t>32355; 35608</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>4737; 11528</t>
+          <t>4737; 11973</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>10664; 22005</t>
+          <t>10979; 22646</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>19878; 32858</t>
+          <t>19519; 33300</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>66024; 74055</t>
+          <t>68859; 74202</t>
         </is>
       </c>
     </row>
@@ -3113,42 +3113,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="I19" s="2" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="J19" s="2" t="inlineStr">
         <is>
           <t>54</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>66</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -3181,42 +3181,42 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>18982</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>20221</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>11376</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>34574</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>10560</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>18437</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>11064</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>31108</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>18982</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>20221</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>11376</t>
-        </is>
-      </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>39980</t>
+          <t>30380</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>71089</t>
+          <t>64953</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>6506; 15346</t>
+          <t>13382; 24882</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>12903; 23969</t>
+          <t>14300; 26124</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>7202; 15540</t>
+          <t>7255; 16202</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>25863; 35698</t>
+          <t>29284; 39285</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>13743; 24573</t>
+          <t>6477; 15882</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>14584; 26540</t>
+          <t>13401; 24598</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>7496; 16565</t>
+          <t>7095; 15203</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>34182; 44853</t>
+          <t>25173; 34973</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>22432; 36715</t>
+          <t>22596; 36815</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>30243; 46642</t>
+          <t>30333; 46602</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>16977; 28954</t>
+          <t>16337; 29174</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>63672; 78607</t>
+          <t>58027; 71785</t>
         </is>
       </c>
     </row>
@@ -3321,42 +3321,42 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
           <t>52</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>59</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="I22" s="2" t="inlineStr">
         <is>
           <t>47</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="J22" s="2" t="inlineStr">
         <is>
           <t>149</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>150</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -3389,42 +3389,42 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>40431</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>44849</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>34774</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>119681</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
           <t>35724</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>42482</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="I23" s="2" t="inlineStr">
         <is>
           <t>32263</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>105556</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>40431</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>44849</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>34774</t>
-        </is>
-      </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>128476</t>
+          <t>102938</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>234032</t>
+          <t>222619</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>28661; 44147</t>
+          <t>32580; 48648</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>33360; 51616</t>
+          <t>35943; 53286</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>24645; 40735</t>
+          <t>26628; 42978</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>97750; 111447</t>
+          <t>111017; 127096</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>33501; 48856</t>
+          <t>28247; 43955</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>36178; 53913</t>
+          <t>34023; 51325</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>26991; 43159</t>
+          <t>24078; 40138</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>111817; 137844</t>
+          <t>95009; 109752</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>64780; 87678</t>
+          <t>65115; 89663</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>74690; 99518</t>
+          <t>74393; 99746</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>56673; 79084</t>
+          <t>55504; 78447</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>215586; 245856</t>
+          <t>211729; 232715</t>
         </is>
       </c>
     </row>
@@ -3529,42 +3529,42 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>179</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
           <t>54</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>42</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="I25" s="2" t="inlineStr">
         <is>
           <t>65</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="J25" s="2" t="inlineStr">
         <is>
           <t>164</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>179</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -3597,42 +3597,42 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>40319</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>41077</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>45283</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>136879</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
           <t>36363</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>28495</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="I26" s="2" t="inlineStr">
         <is>
           <t>41157</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>114765</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>40319</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>41077</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>45283</t>
-        </is>
-      </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>134497</t>
+          <t>122913</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>249262</t>
+          <t>259793</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>29172; 43537</t>
+          <t>33052; 48320</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>22026; 36628</t>
+          <t>33117; 50917</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>32972; 48599</t>
+          <t>36676; 54467</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>107796; 119934</t>
+          <t>127879; 144037</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>32851; 47875</t>
+          <t>29628; 43876</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>33265; 49934</t>
+          <t>21136; 35464</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>36978; 54310</t>
+          <t>33516; 49681</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>125631; 141720</t>
+          <t>115079; 128285</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>65761; 87781</t>
+          <t>66846; 88489</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>58678; 81669</t>
+          <t>58865; 81236</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>74248; 99074</t>
+          <t>75166; 99760</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>237850; 258227</t>
+          <t>247587; 269433</t>
         </is>
       </c>
     </row>
@@ -3737,42 +3737,42 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>297</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>270</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>277</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>765</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
           <t>246</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>241</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="I28" s="2" t="inlineStr">
         <is>
           <t>266</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="J28" s="2" t="inlineStr">
         <is>
           <t>731</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>297</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>270</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>277</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>765</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -3805,42 +3805,42 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>197211</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>189318</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>190343</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>539040</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
           <t>165636</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>169071</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="I29" s="2" t="inlineStr">
         <is>
           <t>179144</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>518745</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>197211</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>189318</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>190343</t>
-        </is>
-      </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>576450</t>
+          <t>487909</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>1095195</t>
+          <t>1026950</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>148119; 182107</t>
+          <t>179147; 213532</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>153097; 186219</t>
+          <t>171369; 208553</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>162427; 199215</t>
+          <t>172936; 210538</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>494793; 542431</t>
+          <t>512446; 559254</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>179464; 214454</t>
+          <t>149198; 182885</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>172497; 208367</t>
+          <t>151473; 186786</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>169476; 207926</t>
+          <t>161254; 195993</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>545068; 601628</t>
+          <t>470432; 505171</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>337770; 388260</t>
+          <t>338740; 388537</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>333254; 384731</t>
+          <t>332062; 381335</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>346326; 396908</t>
+          <t>343486; 397367</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>1053870; 1125460</t>
+          <t>996381; 1055093</t>
         </is>
       </c>
     </row>
